--- a/data/seeds/gen-site-template.xlsx
+++ b/data/seeds/gen-site-template.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="38">
   <si>
     <t>域名(domain)</t>
   </si>
@@ -26,6 +26,12 @@
     <t>公司(companyKey,可选)</t>
   </si>
   <si>
+    <t>竞品类型(competitorType,可选)</t>
+  </si>
+  <si>
+    <t>角色(role,可选:own/competitor)</t>
+  </si>
+  <si>
     <t>渲染(render,可选:ssr/spa/auto)</t>
   </si>
   <si>
@@ -44,6 +50,12 @@
     <t>示例公司</t>
   </si>
   <si>
+    <t>示例类型</t>
+  </si>
+  <si>
+    <t>competitor</t>
+  </si>
+  <si>
     <t>auto</t>
   </si>
   <si>
@@ -71,10 +83,16 @@
     <t>否</t>
   </si>
   <si>
-    <t>详情页示例地址（可选）；提供后模型同时参考详情页结构，生成更准</t>
-  </si>
-  <si>
-    <t>归属公司名（可选）；不填则爬取时按域名兜底</t>
+    <t>详情页示例地址（可选）；提供后模型同时参考详情页结构生成更准，且会尝试识别面包屑产出 categoryFromPage（动态分类）</t>
+  </si>
+  <si>
+    <t>归属公司名（可选）；写入 YAML 顶层 company（同名=同一家公司，多域名共用同一名字）；不填则爬取时按域名兜底</t>
+  </si>
+  <si>
+    <t>竞品类型（可选）；写入 companies.competitor_type，供筛选/分组</t>
+  </si>
+  <si>
+    <t>公司角色（可选）：own=我方 / competitor=竞品；写入 companies.role，缺省 competitor</t>
   </si>
   <si>
     <t>渲染模式：ssr(纯静态) / spa(需浏览器) / auto(自动判断，默认)</t>
@@ -102,6 +120,12 @@
   </si>
   <si>
     <t>5) 每个站点生成后产出 config/sites/&lt;domain&gt;.yaml，再 pnpm probe 验证</t>
+  </si>
+  <si>
+    <t>config/sites/ 目录是爬取范围的唯一真相源（crawl 默认 --source config）：</t>
+  </si>
+  <si>
+    <t>放一个 &lt;domain&gt;.yaml 就爬一个站，删掉就不爬；本 Excel 只是把站点信息喂给模型生成 YAML 的辅助工具。</t>
   </si>
 </sst>
 </file>
@@ -490,17 +514,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="3" width="46" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="24" customWidth="1"/>
-    <col min="6" max="6" width="34" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
+    <col min="6" max="7" width="24" customWidth="1"/>
+    <col min="8" max="8" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -519,25 +544,37 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -548,7 +585,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -558,13 +595,13 @@
   <sheetData>
     <row r="1" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -572,10 +609,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -583,10 +620,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -594,10 +631,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -605,10 +642,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -616,10 +653,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -627,65 +664,109 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
         <v>22</v>
+      </c>
+      <c r="C8" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>29</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/data/seeds/gen-site-template.xlsx
+++ b/data/seeds/gen-site-template.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="41">
   <si>
     <t>域名(domain)</t>
   </si>
@@ -32,6 +32,9 @@
     <t>角色(role,可选:own/competitor)</t>
   </si>
   <si>
+    <t>币种(currency,可选)</t>
+  </si>
+  <si>
     <t>渲染(render,可选:ssr/spa/auto)</t>
   </si>
   <si>
@@ -56,6 +59,9 @@
     <t>competitor</t>
   </si>
   <si>
+    <t>CNY</t>
+  </si>
+  <si>
     <t>auto</t>
   </si>
   <si>
@@ -93,6 +99,9 @@
   </si>
   <si>
     <t>公司角色（可选）：own=我方 / competitor=竞品；写入 companies.role，缺省 competitor</t>
+  </si>
+  <si>
+    <t>站点币种（可选）；写入 products.currency，缺省 CNY；国际站填 USD，中文站可填 元/CNY</t>
   </si>
   <si>
     <t>渲染模式：ssr(纯静态) / spa(需浏览器) / auto(自动判断，默认)</t>
@@ -514,18 +523,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="3" width="46" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
     <col min="5" max="5" width="22" customWidth="1"/>
-    <col min="6" max="7" width="24" customWidth="1"/>
-    <col min="8" max="8" width="34" customWidth="1"/>
+    <col min="6" max="6" width="24" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="24" customWidth="1"/>
+    <col min="9" max="9" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -550,31 +561,37 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -585,7 +602,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -595,13 +612,13 @@
   <sheetData>
     <row r="1" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -609,10 +626,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -620,10 +637,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -631,10 +648,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -642,10 +659,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -653,10 +670,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -664,10 +681,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -675,10 +692,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -686,87 +703,98 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" t="s">
         <v>30</v>
       </c>
-      <c r="C11" t="s">
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C17" t="s">
-        <v>36</v>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C18" t="s">
-        <v>37</v>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/data/seeds/gen-site-template.xlsx
+++ b/data/seeds/gen-site-template.xlsx
@@ -104,7 +104,7 @@
     <t>站点币种（可选）；写入 products.currency，缺省 CNY；国际站填 USD，中文站可填 元/CNY</t>
   </si>
   <si>
-    <t>渲染模式：ssr(纯静态) / spa(需浏览器) / auto(自动判断，默认)</t>
+    <t>渲染模式：ssr(纯静态) / spa(需浏览器) / auto(先 ssr 内容过少回退 spa)。写入 YAML render 字段，供 probe/crawl 统一复用；批量混合 ssr/spa 逐站此列填即可</t>
   </si>
   <si>
     <t>补充说明（可选）；如特殊翻页、需登录等，帮助模型更好生成</t>

--- a/data/seeds/gen-site-template.xlsx
+++ b/data/seeds/gen-site-template.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -529,27 +529,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>acrobiosystems.com</t>
+          <t>promega.com.cn</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.acrobiosystems.com/category/kits-assay-reagents/elisa-kit</t>
+          <t>https://www.promega.com.cn/products/cell-health-assays/inflammation-assay/</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>北京百普赛斯生物科技股份有限公司</t>
+          <t>普洛麦格(北京)生物技术有限公司</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ACROBiosystems 百普赛斯</t>
+          <t>Promega</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -561,22 +561,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>abcam.com</t>
+          <t>rndsystems.com</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://www.abcam.com/en-us/products/primary-antibodies</t>
+          <t>https://www.rndsystems.com/products/elisas/quantikine-colorimetric-sandwich-elisa</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Abcam plc</t>
+          <t>Bio-Techne Corporation (R&amp;D Systems)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Abcam</t>
+          <t>R&amp;D Systems</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -593,22 +593,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>bdbiosciences.com</t>
+          <t>raybiotech.com</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://www.bdbiosciences.com/en-sg/products/reagents/flow-cytometry-reagents/research-reagents</t>
+          <t>https://www.raybiotech.com/elisa-kits-products/sandwich-elisa</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Becton, Dickinson and Company (BD Biosciences)</t>
+          <t>RayBiotech, Inc.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>BD Biosciences</t>
+          <t>RayBiotech</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -625,27 +625,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>beckman.com</t>
+          <t>cas9x.com</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://www.beckman.com/reagents/coulter-flow-cytometry/antibodies-and-kits</t>
+          <t>https://www.cas9x.com/bdxb</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Beckman Coulter, Inc.</t>
+          <t>苏州海星生物科技有限公司</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Beckman Coulter</t>
+          <t>cas9x 海星生物</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -657,22 +657,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>cellsignal.com</t>
+          <t>acrobiosystems.com</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://www.cellsignal.com/browse?tab=product&amp;categories=Primary%20Antibodies</t>
+          <t>https://www.acrobiosystems.com/category/kits-assay-reagents/elisa-kit</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Cell Signaling Technology, Inc.</t>
+          <t>北京百普赛斯生物科技股份有限公司</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CST</t>
+          <t>ACROBiosystems 百普赛斯</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -681,518 +681,6 @@
         </is>
       </c>
       <c r="I6" t="inlineStr">
-        <is>
-          <t>browser</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>caymanchem.com</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>https://www.caymanchem.com/assays</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Cayman Chemical Company</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Cayman Chemical</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>browser</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>miltenyibiotec.com</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>https://www.miltenyibiotec.com/US-en/products/macs-cell-separation.html</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Miltenyi Biotec GmbH</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Miltenyi</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>browser</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>promega.com.cn</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>https://www.promega.com.cn/products/cell-health-assays/</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>普洛麦格(北京)生物技术有限公司</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Promega</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>browser</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>rndsystems.com</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>https://www.rndsystems.com/products/elisas</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Bio-Techne Corporation (R&amp;D Systems)</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>R&amp;D Systems</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>browser</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>raybiotech.com</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>https://www.raybiotech.com/elisa-kits</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>RayBiotech, Inc.</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>RayBiotech</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>browser</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>sciencellonline.com</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>https://sciencellonline.com/en/products-services/cell-culture-media/</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>ScienCell Research Laboratories, Inc.</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>ScienCell</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>browser</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>selleckchem.com</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>https://www.selleckchem.com/screening-libraries.html</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Selleck Chemicals LLC</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Selleck</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>browser</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>basalmedia.com</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>https://www.basalmedia.com/</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>上海源培生物科技股份有限公司</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>BasalMedia 源培生物</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>browser</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>senbeijia.com</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>http://www.senbeijia.com/category.php?id=58</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>南京森贝伽生物科技有限公司</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Senbeijia 森贝伽</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>browser</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>dojindo.cn</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>https://www.dojindo.cn/#/index</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>同仁化学研究所 (Dojindo Laboratories)</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Dojindo 同仁化学</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>browser</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>corning.com</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>https://www.corning.com/cn/zh/products/life-sciences/products/cell-Culture.html</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Corning Incorporated (Corning Life Sciences)</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Corning</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>browser</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>lonsera.cn</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>https://www.lonsera.cn/list_11/</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>苏州双洳生物科技有限公司</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Lonsera 双洳生物</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>browser</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>cas9x.com</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>https://www.cas9x.com/bdxb</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>苏州海星生物科技有限公司</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>cas9x 海星生物</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>browser</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>thermofisher.com</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>https://www.thermofisher.com/mx/en/home/life-science/antibodies/ebioscience.html</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Thermo Fisher Scientific Inc.</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Thermo Fisher</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>browser</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>novoprotein.com.cn</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>https://www.novoprotein.com.cn/products</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>苏州近岸蛋白质科技股份有限公司</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Novoprotein 近岸蛋白</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>browser</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>genscript.com</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>https://www.genscript.com/catalog-antibody-products.html</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>南京金斯瑞生物科技有限公司</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>GenScript 金斯瑞</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
         <is>
           <t>browser</t>
         </is>
@@ -1410,7 +898,6 @@
           <t>使用步骤</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>1) 在「站点清单」按列填入真实站点（删除示例行）</t>
@@ -1418,8 +905,6 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>2) 运行 pnpm gen-site:batch  （默认读取 data/seeds/gen-site-template.xlsx）</t>
@@ -1427,8 +912,6 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>3) 可用 pnpm gen-site:batch --file &lt;路径&gt; 指定其它 Excel</t>
@@ -1436,8 +919,6 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
           <t>4) 加 --dry-run 仅解析并打印待生成清单，不调用模型</t>
@@ -1445,22 +926,18 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
           <t>5) 每个站点生成后产出 config/sites/&lt;domain&gt;.yaml，再 pnpm probe 验证</t>
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
           <t>config/sites/ 目录是爬取范围的唯一真相源（crawl 默认 --source config）：</t>
@@ -1468,8 +945,6 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
           <t>放一个 &lt;domain&gt;.yaml 就爬一个站，删掉就不爬；本 Excel 只是把站点信息喂给模型生成 YAML 的辅助工具。</t>

--- a/data/seeds/gen-site-template.xlsx
+++ b/data/seeds/gen-site-template.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -529,22 +529,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>promega.com.cn</t>
+          <t>www.dojindo.cn</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.promega.com.cn/products/cell-health-assays/inflammation-assay/</t>
+          <t>https://www.dojindo.cn/products/category/13</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>普洛麦格(北京)生物技术有限公司</t>
+          <t>同仁化学研究所 (Dojindo Laboratories)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Promega</t>
+          <t>Dojindo 同仁化学</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -553,134 +553,6 @@
         </is>
       </c>
       <c r="I2" t="inlineStr">
-        <is>
-          <t>browser</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>rndsystems.com</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>https://www.rndsystems.com/products/elisas/quantikine-colorimetric-sandwich-elisa</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Bio-Techne Corporation (R&amp;D Systems)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>R&amp;D Systems</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>browser</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>raybiotech.com</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>https://www.raybiotech.com/elisa-kits-products/sandwich-elisa</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>RayBiotech, Inc.</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>RayBiotech</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>browser</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>cas9x.com</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>https://www.cas9x.com/bdxb</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>苏州海星生物科技有限公司</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>cas9x 海星生物</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>browser</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>acrobiosystems.com</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>https://www.acrobiosystems.com/category/kits-assay-reagents/elisa-kit</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>北京百普赛斯生物科技股份有限公司</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>ACROBiosystems 百普赛斯</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
         <is>
           <t>browser</t>
         </is>
@@ -735,7 +607,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>站点域名，如 www.xpbiomed.com；执行后会生成 config/sites/&lt;domain&gt;.yaml</t>
+          <t>站点域名 = 列表页URL的完整 host（必须带 www 等子域，一个字符都不能省；非 80/443 端口须带端口号，如 example.com:8080）；执行后会生成 config/sites/&lt;domain&gt;.yaml</t>
         </is>
       </c>
     </row>
@@ -892,6 +764,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
@@ -932,6 +805,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
